--- a/data/trans_bre/P23_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P23_R2-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-24,33; -17,44</t>
+          <t>-24,44; -17,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,71; -13,38</t>
+          <t>-21,01; -13,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,71; -11,84</t>
+          <t>-20,63; -12,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,46; -12,98</t>
+          <t>-21,36; -12,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-67,28; -54,8</t>
+          <t>-67,23; -54,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,83; -45,13</t>
+          <t>-61,08; -46,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,03; -44,02</t>
+          <t>-62,75; -43,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-69,52; -52,64</t>
+          <t>-69,4; -52,79</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -8,55</t>
+          <t>-15,51; -8,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,72; -1,27</t>
+          <t>-8,26; -1,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,5; -2,58</t>
+          <t>-8,89; -2,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 3,75</t>
+          <t>-11,09; 2,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,05; -19,76</t>
+          <t>-32,64; -19,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,66; -3,52</t>
+          <t>-19,73; -3,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,09; -6,95</t>
+          <t>-21,72; -6,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,41; 14,87</t>
+          <t>-38,6; 7,14</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,6; -1,06</t>
+          <t>-12,18; -0,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 4,22</t>
+          <t>-8,92; 4,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 2,34</t>
+          <t>-8,03; 2,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 4,3</t>
+          <t>-4,55; 4,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,01; -3,58</t>
+          <t>-33,59; -2,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 14,89</t>
+          <t>-25,2; 15,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 10,64</t>
+          <t>-28,73; 12,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 32,08</t>
+          <t>-24,83; 30,61</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,45; -12,85</t>
+          <t>-17,6; -13,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,9; -7,38</t>
+          <t>-12,22; -7,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,64; -6,23</t>
+          <t>-10,66; -6,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,57; -0,24</t>
+          <t>-9,79; -0,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,77; -33,23</t>
+          <t>-42,63; -34,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,33; -20,55</t>
+          <t>-32,08; -21,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,86; -18,53</t>
+          <t>-29,78; -18,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,58; -4,27</t>
+          <t>-38,2; -8,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P23_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P23_R2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-16,98</t>
+          <t>-15,87</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-61,93%</t>
+          <t>-60,23%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-24,44; -17,9</t>
+          <t>-24,42; -17,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,01; -13,86</t>
+          <t>-21,2; -13,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,63; -12,32</t>
+          <t>-19,78; -11,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,36; -12,88</t>
+          <t>-20,02; -11,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-67,23; -54,77</t>
+          <t>-67,44; -54,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-61,08; -46,82</t>
+          <t>-61,42; -46,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,75; -43,74</t>
+          <t>-61,68; -44,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-69,4; -52,79</t>
+          <t>-68,3; -51,01</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,98</t>
+          <t>-5,5</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-19,35%</t>
+          <t>-19,2%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,51; -8,69</t>
+          <t>-15,67; -8,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,26; -1,54</t>
+          <t>-7,87; -1,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -2,39</t>
+          <t>-8,66; -2,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 2,31</t>
+          <t>-8,41; -2,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,64; -19,66</t>
+          <t>-32,99; -20,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,73; -3,89</t>
+          <t>-18,35; -3,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,72; -6,19</t>
+          <t>-21,41; -7,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,6; 7,14</t>
+          <t>-27,12; -9,76</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,18; -0,88</t>
+          <t>-12,75; -0,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 4,4</t>
+          <t>-9,42; 3,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 2,64</t>
+          <t>-8,04; 2,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 4,24</t>
+          <t>-3,99; 4,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,59; -2,91</t>
+          <t>-34,44; -2,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 15,45</t>
+          <t>-25,9; 12,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 12,95</t>
+          <t>-28,99; 12,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 30,61</t>
+          <t>-22,42; 32,56</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,34</t>
+          <t>-6,66</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-26,24%</t>
+          <t>-26,0%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,6; -13,2</t>
+          <t>-17,47; -13,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -7,44</t>
+          <t>-12,1; -7,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,66; -6,25</t>
+          <t>-10,89; -6,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,79; -0,84</t>
+          <t>-8,84; -4,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,63; -34,13</t>
+          <t>-42,89; -34,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,08; -21,21</t>
+          <t>-31,94; -20,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,78; -18,62</t>
+          <t>-30,38; -18,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,2; -8,24</t>
+          <t>-32,68; -18,61</t>
         </is>
       </c>
     </row>
